--- a/Encuestas de Satisfacción/Supervisor ev. por el equipo Pedagógico/Equipo pedagog al supervisoor.xlsx
+++ b/Encuestas de Satisfacción/Supervisor ev. por el equipo Pedagógico/Equipo pedagog al supervisoor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Benjo\Prácticas Laborales I\Reportes Automáticos\encuestas_app\Encuestas de Satisfacción\Supervisor ev. por el equipo Pedagógico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599CD79-A7C8-4F9D-8171-7B382A77ECAA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C38AC2A-37F1-4E88-B257-A8333A374503}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4925303F-CABA-47DD-A2B2-66CC59339261}"/>
+    <workbookView xWindow="5232" yWindow="312" windowWidth="11472" windowHeight="12048" xr2:uid="{4925303F-CABA-47DD-A2B2-66CC59339261}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -48,15 +48,9 @@
     <t>FECHA FIN: Friday, 3 de July de 2026, 23:55</t>
   </si>
   <si>
-    <t>RESPUESTAS ENVIADAS: 140</t>
-  </si>
-  <si>
     <t>Wednesday, 3 de June de 2026, 15:22</t>
   </si>
   <si>
-    <t>Preguntas: 19</t>
-  </si>
-  <si>
     <t>Etiqueta</t>
   </si>
   <si>
@@ -136,6 +130,12 @@
   </si>
   <si>
     <t>EVALUACIÓN DEL EQUIPO PEDAGÓGICO AL SUPERVISOR</t>
+  </si>
+  <si>
+    <t>RESPUESTAS ENVIADAS: 10</t>
+  </si>
+  <si>
+    <t>Preguntas: 15</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -559,61 +559,61 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="J14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4">
         <v>8</v>
@@ -637,7 +637,7 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4">
         <v>8</v>
@@ -661,7 +661,7 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4">
         <v>8</v>
@@ -685,7 +685,7 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4">
         <v>8</v>
@@ -709,7 +709,7 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
         <v>8</v>
@@ -733,7 +733,7 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
         <v>8</v>
@@ -757,7 +757,7 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
         <v>8</v>
@@ -781,7 +781,7 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4">
         <v>8</v>
@@ -805,7 +805,7 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4">
         <v>8</v>
@@ -829,7 +829,7 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="4">
         <v>8</v>
@@ -853,7 +853,7 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="4">
         <v>8</v>
@@ -877,7 +877,7 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4">
         <v>8</v>
@@ -901,7 +901,7 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
         <v>8</v>
@@ -925,7 +925,7 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4">
         <v>8</v>
@@ -949,10 +949,10 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4"/>
@@ -964,7 +964,7 @@
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
@@ -976,7 +976,7 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="4"/>

--- a/Encuestas de Satisfacción/Supervisor ev. por el equipo Pedagógico/Equipo pedagog al supervisoor.xlsx
+++ b/Encuestas de Satisfacción/Supervisor ev. por el equipo Pedagógico/Equipo pedagog al supervisoor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Benjo\Prácticas Laborales I\Reportes Automáticos\encuestas_app\Encuestas de Satisfacción\Supervisor ev. por el equipo Pedagógico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C38AC2A-37F1-4E88-B257-A8333A374503}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8443E9-EB6B-4620-A2B4-5BFCC746F1F1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5232" yWindow="312" windowWidth="11472" windowHeight="12048" xr2:uid="{4925303F-CABA-47DD-A2B2-66CC59339261}"/>
+    <workbookView xWindow="1080" yWindow="312" windowWidth="11472" windowHeight="12048" xr2:uid="{4925303F-CABA-47DD-A2B2-66CC59339261}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -516,6 +516,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E780FD97-A90E-4E56-A0C0-6108043610CB}">
   <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="123" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
